--- a/Measurement.xlsx
+++ b/Measurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gajaj\Desktop\School\Bachelor\graph_databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF6AA7A-1E35-4139-BFD4-CDAA0CF3BCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134E1474-BF49-430A-96EE-605745293B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>Neo4j</t>
   </si>
@@ -92,9 +92,6 @@
     <t>delete all</t>
   </si>
   <si>
-    <t>spočítá všechny sousedy do hloubky 5</t>
-  </si>
-  <si>
     <t>výsledek</t>
   </si>
   <si>
@@ -107,14 +104,14 @@
     <t>spočítá všechny sousedy vrcholu s id 1 do hloubky 4</t>
   </si>
   <si>
-    <t>další měření</t>
+    <t>spočítá všechny sousedy vrcholu s id 1 do hloubky 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,19 +135,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,12 +151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -228,21 +213,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7063,17 +7042,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A794442-7EDD-4B7F-9E93-0359649CCCF5}">
-  <dimension ref="A2:M40"/>
+  <dimension ref="A3:M40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>13</v>
@@ -7089,12 +7063,6 @@
       </c>
       <c r="F3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7116,9 +7084,6 @@
       <c r="F4" s="1">
         <v>63.691000000000003</v>
       </c>
-      <c r="H4" s="4">
-        <v>103.223</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -7136,12 +7101,6 @@
       <c r="E5" s="1">
         <v>147.721</v>
       </c>
-      <c r="H5">
-        <v>57.3</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -7161,20 +7120,20 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -7214,7 +7173,7 @@
         <v>8</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -7339,7 +7298,7 @@
         <f>AVERAGE(B13:K13)</f>
         <v>2.4199999999999999E-2</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="1">
         <v>7176</v>
       </c>
     </row>
@@ -7386,20 +7345,20 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -7439,7 +7398,7 @@
         <v>8</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -7564,7 +7523,7 @@
         <f>AVERAGE(B20:K20)</f>
         <v>5.3864000000000001</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="1">
         <v>240949</v>
       </c>
     </row>
@@ -7611,20 +7570,20 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -7664,7 +7623,7 @@
         <v>8</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -7836,20 +7795,20 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -7889,7 +7848,7 @@
         <v>8</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -8007,7 +7966,7 @@
       <c r="J34" s="1">
         <v>77.981999999999999</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="4">
         <v>82.072999999999993</v>
       </c>
       <c r="L34" s="1">
@@ -8061,69 +8020,69 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="B37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="B38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="B39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="B40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B9:M9"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G38"/>
     <mergeCell ref="B39:G39"/>
     <mergeCell ref="B40:G40"/>
     <mergeCell ref="B30:M30"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B9:M9"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Measurement.xlsx
+++ b/Measurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gajaj\Desktop\School\Bachelor\graph_databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134E1474-BF49-430A-96EE-605745293B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FEB104-6385-477C-9935-45AE247581DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
   </bookViews>
@@ -219,13 +219,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -778,34 +778,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.17199999999999999</c:v>
+                  <c:v>0.16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20100000000000001</c:v>
+                  <c:v>0.182</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.219</c:v>
+                  <c:v>0.17399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.187</c:v>
+                  <c:v>0.19600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.86</c:v>
+                  <c:v>0.19</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.23400000000000001</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.25</c:v>
+                  <c:v>0.191</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.20300000000000001</c:v>
+                  <c:v>0.16400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.20300000000000001</c:v>
+                  <c:v>0.19700000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.23400000000000001</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1400,34 +1400,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>9.5960000000000001</c:v>
+                  <c:v>6.2539999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9090000000000007</c:v>
+                  <c:v>7.0019999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.9260000000000002</c:v>
+                  <c:v>6.9569999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.1210000000000004</c:v>
+                  <c:v>7.048</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.1129999999999995</c:v>
+                  <c:v>6.8529999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.1270000000000007</c:v>
+                  <c:v>7.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.0960000000000001</c:v>
+                  <c:v>6.702</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.9380000000000006</c:v>
+                  <c:v>6.4059999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.9719999999999995</c:v>
+                  <c:v>6.6239999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.8469999999999995</c:v>
+                  <c:v>6.4660000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2115,34 +2115,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>77.686000000000007</c:v>
+                  <c:v>50.683</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>83.85</c:v>
+                  <c:v>53.917999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>79.082999999999998</c:v>
+                  <c:v>51.317</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84</c:v>
+                  <c:v>50.415999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.662999999999997</c:v>
+                  <c:v>50.917999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>78.150000000000006</c:v>
+                  <c:v>50.692999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>77.89</c:v>
+                  <c:v>50.76</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>78.802999999999997</c:v>
+                  <c:v>50.936</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82.501999999999995</c:v>
+                  <c:v>50.365000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>77.081000000000003</c:v>
+                  <c:v>52.921999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2826,34 +2826,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>112.67</c:v>
+                  <c:v>72.956999999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>111.092</c:v>
+                  <c:v>74.742999999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>113.52</c:v>
+                  <c:v>78.183000000000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>112.83799999999999</c:v>
+                  <c:v>73.454999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>113.965</c:v>
+                  <c:v>70.302999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>121.44199999999999</c:v>
+                  <c:v>71.822000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>111.286</c:v>
+                  <c:v>71.528999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>109.86499999999999</c:v>
+                  <c:v>72.44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>114.498</c:v>
+                  <c:v>70.861999999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>109.206</c:v>
+                  <c:v>72.620999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7120,20 +7120,20 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -7307,58 +7307,58 @@
         <v>6</v>
       </c>
       <c r="B14" s="1">
-        <v>0.17199999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="C14" s="1">
-        <v>0.20100000000000001</v>
+        <v>0.182</v>
       </c>
       <c r="D14" s="1">
-        <v>0.219</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="E14" s="1">
-        <v>0.187</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>0.86</v>
+        <v>0.19</v>
       </c>
       <c r="G14" s="1">
-        <v>0.23400000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H14" s="1">
-        <v>0.25</v>
+        <v>0.191</v>
       </c>
       <c r="I14" s="1">
-        <v>0.20300000000000001</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="J14" s="1">
-        <v>0.20300000000000001</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="K14" s="1">
-        <v>0.23400000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="L14" s="1">
         <f>AVERAGE(B14:K14)</f>
-        <v>0.27629999999999993</v>
+        <v>0.18139999999999998</v>
       </c>
       <c r="M14" s="1">
         <v>7176</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -7532,58 +7532,58 @@
         <v>6</v>
       </c>
       <c r="B21" s="1">
-        <v>9.5960000000000001</v>
+        <v>6.2539999999999996</v>
       </c>
       <c r="C21" s="1">
-        <v>8.9090000000000007</v>
+        <v>7.0019999999999998</v>
       </c>
       <c r="D21" s="1">
-        <v>8.9260000000000002</v>
+        <v>6.9569999999999999</v>
       </c>
       <c r="E21" s="1">
-        <v>9.1210000000000004</v>
+        <v>7.048</v>
       </c>
       <c r="F21" s="1">
-        <v>9.1129999999999995</v>
+        <v>6.8529999999999998</v>
       </c>
       <c r="G21" s="1">
-        <v>9.1270000000000007</v>
+        <v>7.1289999999999996</v>
       </c>
       <c r="H21" s="1">
-        <v>9.0960000000000001</v>
+        <v>6.702</v>
       </c>
       <c r="I21" s="1">
-        <v>8.9380000000000006</v>
+        <v>6.4059999999999997</v>
       </c>
       <c r="J21" s="1">
-        <v>8.9719999999999995</v>
+        <v>6.6239999999999997</v>
       </c>
       <c r="K21" s="1">
-        <v>8.8469999999999995</v>
+        <v>6.4660000000000002</v>
       </c>
       <c r="L21" s="1">
         <f>AVERAGE(B21:K21)</f>
-        <v>9.0644999999999989</v>
+        <v>6.7441000000000004</v>
       </c>
       <c r="M21" s="1">
         <v>240949</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -7757,58 +7757,58 @@
         <v>6</v>
       </c>
       <c r="B28" s="1">
-        <v>77.686000000000007</v>
+        <v>50.683</v>
       </c>
       <c r="C28" s="1">
-        <v>83.85</v>
+        <v>53.917999999999999</v>
       </c>
       <c r="D28" s="1">
-        <v>79.082999999999998</v>
+        <v>51.317</v>
       </c>
       <c r="E28" s="1">
-        <v>84</v>
+        <v>50.415999999999997</v>
       </c>
       <c r="F28" s="1">
-        <v>77.662999999999997</v>
+        <v>50.917999999999999</v>
       </c>
       <c r="G28" s="1">
-        <v>78.150000000000006</v>
+        <v>50.692999999999998</v>
       </c>
       <c r="H28" s="1">
-        <v>77.89</v>
+        <v>50.76</v>
       </c>
       <c r="I28" s="1">
-        <v>78.802999999999997</v>
+        <v>50.936</v>
       </c>
       <c r="J28" s="1">
-        <v>82.501999999999995</v>
+        <v>50.365000000000002</v>
       </c>
       <c r="K28" s="1">
-        <v>77.081000000000003</v>
+        <v>52.921999999999997</v>
       </c>
       <c r="L28" s="1">
         <f>AVERAGE(B28:K28)</f>
-        <v>79.6708</v>
+        <v>51.2928</v>
       </c>
       <c r="M28" s="1">
         <v>814122</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -7982,38 +7982,38 @@
         <v>6</v>
       </c>
       <c r="B35" s="1">
-        <v>112.67</v>
+        <v>72.956999999999994</v>
       </c>
       <c r="C35" s="1">
-        <v>111.092</v>
+        <v>74.742999999999995</v>
       </c>
       <c r="D35" s="1">
-        <v>113.52</v>
+        <v>78.183000000000007</v>
       </c>
       <c r="E35" s="1">
-        <v>112.83799999999999</v>
+        <v>73.454999999999998</v>
       </c>
       <c r="F35" s="1">
-        <v>113.965</v>
+        <v>70.302999999999997</v>
       </c>
       <c r="G35" s="1">
-        <v>121.44199999999999</v>
+        <v>71.822000000000003</v>
       </c>
       <c r="H35" s="1">
-        <v>111.286</v>
+        <v>71.528999999999996</v>
       </c>
       <c r="I35" s="1">
-        <v>109.86499999999999</v>
+        <v>72.44</v>
       </c>
       <c r="J35" s="1">
-        <v>114.498</v>
+        <v>70.861999999999995</v>
       </c>
       <c r="K35" s="1">
-        <v>109.206</v>
+        <v>72.620999999999995</v>
       </c>
       <c r="L35" s="1">
         <f>AVERAGE(B35:K35)</f>
-        <v>113.0382</v>
+        <v>72.891499999999994</v>
       </c>
       <c r="M35" s="1">
         <v>1051030</v>
@@ -8023,64 +8023,64 @@
       <c r="A37" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B30:M30"/>
     <mergeCell ref="B23:M23"/>
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="B9:M9"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B30:M30"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Measurement.xlsx
+++ b/Measurement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gajaj\Desktop\School\Bachelor\graph_databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FEB104-6385-477C-9935-45AE247581DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078C74EB-3859-4BEF-AF93-C143EAB8A83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="32">
   <si>
     <t>Neo4j</t>
   </si>
@@ -89,9 +89,6 @@
     <t>delete E</t>
   </si>
   <si>
-    <t>delete all</t>
-  </si>
-  <si>
     <t>výsledek</t>
   </si>
   <si>
@@ -106,12 +103,42 @@
   <si>
     <t>spočítá všechny sousedy vrcholu s id 1 do hloubky 5</t>
   </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>najde nejkratší orientovanou cestu z vrcholu s id 12000 do vrcholu s id 1047, přičemž cesta neexistuje</t>
+  </si>
+  <si>
+    <t>najde nejkratší neorientovanou cestu mezi dvěma vrcholy s id 12000 a 1047</t>
+  </si>
+  <si>
+    <t>insert Vertices</t>
+  </si>
+  <si>
+    <t>insert Edges</t>
+  </si>
+  <si>
+    <t>delete Vertices</t>
+  </si>
+  <si>
+    <t>delete Edges</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +166,20 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD5D6D6"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -213,12 +254,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -228,6 +270,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -259,14 +302,268 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Neo4j</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>insert V</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>insert E</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>delete V</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>delete E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>26.324399999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>133.3544</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.138799999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.202000000000012</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8CDD-41E0-99BA-4AE19DA0EA06}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ArangoDB</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>insert V</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>insert E</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>delete V</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>delete E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$3:$E$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>26.611700000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.8934</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.071199999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>167.40899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8CDD-41E0-99BA-4AE19DA0EA06}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OrientDB</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>insert V</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>insert E</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>delete V</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>delete E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>105.69579999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>763.62980000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>106.29249999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>671.24500000000012</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8CDD-41E0-99BA-4AE19DA0EA06}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1101099183"/>
+        <c:axId val="879286847"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1101099183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -278,14 +575,141 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:rPr lang="cs-CZ"/>
-              <a:t>Q1</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-GB"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
-        </c:rich>
-      </c:tx>
+        </c:txPr>
+        <c:crossAx val="879286847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879286847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="800"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Čas [s]</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1101099183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="100"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -299,7 +723,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -314,8 +738,76 @@
           <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -326,7 +818,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$11</c:f>
+              <c:f>Sheet1!$A$32</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -352,11 +844,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$L$10</c15:sqref>
+                    <c15:sqref>Sheet1!$B$31:$L$31</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$10:$K$10</c:f>
+              <c:f>Sheet1!$B$31:$K$31</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -397,11 +889,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$11:$L$11</c15:sqref>
+                    <c15:sqref>Sheet1!$B$32:$L$32</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$11:$K$11</c:f>
+              <c:f>Sheet1!$B$32:$K$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -450,7 +942,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$12</c:f>
+              <c:f>Sheet1!$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -476,11 +968,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$L$10</c15:sqref>
+                    <c15:sqref>Sheet1!$B$31:$L$31</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$10:$K$10</c:f>
+              <c:f>Sheet1!$B$31:$K$31</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -521,11 +1013,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$12:$L$12</c15:sqref>
+                    <c15:sqref>Sheet1!$B$33:$L$33</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$12:$K$12</c:f>
+              <c:f>Sheet1!$B$33:$K$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -574,7 +1066,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$13</c:f>
+              <c:f>Sheet1!$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -600,11 +1092,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$L$10</c15:sqref>
+                    <c15:sqref>Sheet1!$B$31:$L$31</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$10:$K$10</c:f>
+              <c:f>Sheet1!$B$31:$K$31</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -645,11 +1137,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$13:$L$13</c15:sqref>
+                    <c15:sqref>Sheet1!$B$34:$L$34</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$13:$K$13</c:f>
+              <c:f>Sheet1!$B$34:$K$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -698,7 +1190,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$14</c:f>
+              <c:f>Sheet1!$A$35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -724,11 +1216,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$10:$L$10</c15:sqref>
+                    <c15:sqref>Sheet1!$B$31:$L$31</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$10:$K$10</c:f>
+              <c:f>Sheet1!$B$31:$K$31</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -769,11 +1261,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$14:$L$14</c15:sqref>
+                    <c15:sqref>Sheet1!$B$35:$L$35</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$B$14:$K$14</c:f>
+              <c:f>Sheet1!$B$35:$K$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -836,6 +1328,62 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Pokus</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -857,8 +1405,8 @@
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:pPr algn="ctr">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -908,7 +1456,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -941,7 +1489,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -972,8 +1520,8 @@
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:pPr algn="ctr">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1001,7 +1549,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1015,7 +1563,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1061,8 +1609,18 @@
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
-      <a:pPr>
-        <a:defRPr/>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -1075,7 +1633,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1089,63 +1647,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="cs-CZ"/>
-              <a:t>Q2</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-GB"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -1156,7 +1658,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$18</c:f>
+              <c:f>Sheet1!$A$39</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1179,7 +1681,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$18:$K$18</c:f>
+              <c:f>Sheet1!$B$39:$K$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1228,7 +1730,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$19</c:f>
+              <c:f>Sheet1!$A$40</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1251,7 +1753,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$19:$K$19</c:f>
+              <c:f>Sheet1!$B$40:$K$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1300,7 +1802,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$20</c:f>
+              <c:f>Sheet1!$A$41</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1323,7 +1825,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$20:$K$20</c:f>
+              <c:f>Sheet1!$B$41:$K$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1372,7 +1874,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$21</c:f>
+              <c:f>Sheet1!$A$42</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1395,7 +1897,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$21:$K$21</c:f>
+              <c:f>Sheet1!$B$42:$K$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1461,7 +1963,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$A$17</c15:sqref>
+                          <c15:sqref>Sheet1!$A$38</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1490,7 +1992,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$B$17:$K$17</c15:sqref>
+                          <c15:sqref>Sheet1!$B$38:$K$38</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1548,6 +2050,62 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Pokus</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1569,7 +2127,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1619,7 +2177,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1633,11 +2191,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="cs-CZ"/>
-                  <a:t>Čas</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="cs-CZ" baseline="0"/>
-                  <a:t> [s]</a:t>
+                  <a:t>Čas [s]</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-GB"/>
               </a:p>
@@ -1656,7 +2210,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1688,7 +2242,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1716,7 +2270,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1730,7 +2284,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1776,8 +2330,18 @@
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
-      <a:pPr>
-        <a:defRPr/>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -1790,7 +2354,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1804,63 +2368,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="cs-CZ"/>
-              <a:t>Q3</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-GB"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -1871,7 +2379,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$25</c:f>
+              <c:f>Sheet1!$A$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1894,7 +2402,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$25:$K$25</c:f>
+              <c:f>Sheet1!$B$46:$K$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1943,7 +2451,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$26</c:f>
+              <c:f>Sheet1!$A$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1966,7 +2474,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$26:$K$26</c:f>
+              <c:f>Sheet1!$B$47:$K$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2015,7 +2523,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$27</c:f>
+              <c:f>Sheet1!$A$48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2038,7 +2546,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$27:$K$27</c:f>
+              <c:f>Sheet1!$B$48:$K$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2087,7 +2595,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$28</c:f>
+              <c:f>Sheet1!$A$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2110,7 +2618,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$28:$K$28</c:f>
+              <c:f>Sheet1!$B$49:$K$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2176,7 +2684,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$A$24</c15:sqref>
+                          <c15:sqref>Sheet1!$A$45</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2205,7 +2713,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$B$24:$K$24</c15:sqref>
+                          <c15:sqref>Sheet1!$B$45:$K$45</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2263,6 +2771,62 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Pokus</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2284,7 +2848,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2334,7 +2898,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2367,7 +2931,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2399,7 +2963,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2427,7 +2991,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2441,7 +3005,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2487,8 +3051,18 @@
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
-      <a:pPr>
-        <a:defRPr/>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2501,7 +3075,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2515,63 +3089,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="cs-CZ"/>
-              <a:t>Q4</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-GB"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -2582,7 +3100,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$32</c:f>
+              <c:f>Sheet1!$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2605,7 +3123,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$32:$K$32</c:f>
+              <c:f>Sheet1!$B$53:$K$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2654,7 +3172,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$33</c:f>
+              <c:f>Sheet1!$A$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2677,7 +3195,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$33:$K$33</c:f>
+              <c:f>Sheet1!$B$54:$K$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2726,7 +3244,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$34</c:f>
+              <c:f>Sheet1!$A$55</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2749,7 +3267,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$34:$K$34</c:f>
+              <c:f>Sheet1!$B$55:$K$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2798,7 +3316,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$35</c:f>
+              <c:f>Sheet1!$A$56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2821,7 +3339,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$35:$K$35</c:f>
+              <c:f>Sheet1!$B$56:$K$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2887,7 +3405,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$A$31</c15:sqref>
+                          <c15:sqref>Sheet1!$A$52</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2916,7 +3434,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$B$31:$K$31</c15:sqref>
+                          <c15:sqref>Sheet1!$B$52:$K$52</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2974,6 +3492,62 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Pokus</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2995,7 +3569,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3045,7 +3619,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -3078,7 +3652,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -3109,8 +3683,8 @@
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:pPr algn="ctr">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3138,7 +3712,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3152,7 +3726,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3198,8 +3772,18 @@
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
-      <a:pPr>
-        <a:defRPr/>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -3212,7 +3796,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3226,279 +3810,297 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="cs-CZ"/>
-              <a:t>Insert/Delete</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-GB"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>Sheet1!$A$60</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Neo4j</c:v>
+                  <c:v>Cypher</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$B$3:$E$3</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>insert V</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>insert E</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>delete V</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>delete E</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$E$4</c:f>
+              <c:f>Sheet1!$B$60:$K$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>36</c:v>
+                  <c:v>6.3E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>183</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.135999999999999</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.536999999999999</c:v>
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.8000000000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8CDD-41E0-99BA-4AE19DA0EA06}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ArangoDB</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$B$3:$E$3</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>insert V</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>insert E</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>delete V</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>delete E</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$5:$E$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>29.62</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>147.721</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8CDD-41E0-99BA-4AE19DA0EA06}"/>
+              <c16:uniqueId val="{00000001-5092-4D4E-9551-B404343B250F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>Sheet1!$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>OrientDB</c:v>
+                  <c:v>AQL</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$B$3:$E$3</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>insert V</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>insert E</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>delete V</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>delete E</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$6:$E$6</c:f>
+              <c:f>Sheet1!$B$61:$K$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>68</c:v>
+                  <c:v>6.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1041</c:v>
+                  <c:v>1E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>97</c:v>
+                  <c:v>1E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1159</c:v>
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8CDD-41E0-99BA-4AE19DA0EA06}"/>
+              <c16:uniqueId val="{00000002-5092-4D4E-9551-B404343B250F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$62</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gremlin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$62:$K$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.217</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.6999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5092-4D4E-9551-B404343B250F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$63</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SQL - OrientDB</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$63:$K$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.03</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5092-4D4E-9551-B404343B250F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3510,18 +4112,73 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="1101099183"/>
-        <c:axId val="879286847"/>
-      </c:barChart>
+        <c:smooth val="0"/>
+        <c:axId val="106719536"/>
+        <c:axId val="106720016"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="1101099183"/>
+        <c:axId val="106719536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Pokus</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3543,7 +4200,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3558,7 +4215,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="879286847"/>
+        <c:crossAx val="106720016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3566,12 +4223,12 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="879286847"/>
+        <c:axId val="106720016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -3589,11 +4246,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -3622,11 +4279,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -3658,7 +4315,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3673,7 +4330,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1101099183"/>
+        <c:crossAx val="106719536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3686,7 +4343,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3700,7 +4357,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3746,8 +4403,589 @@
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
-      <a:pPr>
-        <a:defRPr/>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$67</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cypher</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$67:$K$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-13D3-48BB-A6DC-F05ECBE88979}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AQL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$68:$K$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-13D3-48BB-A6DC-F05ECBE88979}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$69</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gremlin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$69:$K$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-13D3-48BB-A6DC-F05ECBE88979}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$70</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SQL - OrientDB</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$70:$K$70</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.0569999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.88</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8109999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7909999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9339999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7889999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8109999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7649999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-13D3-48BB-A6DC-F05ECBE88979}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="814621936"/>
+        <c:axId val="814622416"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="814621936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Pokus</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814622416"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="814622416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Čas [s]</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="814621936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr algn="ctr">
+        <a:defRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -3960,6 +5198,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -6025,6 +7343,1038 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6545,22 +8895,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>83287</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2FCDC96-0381-AB8B-AACD-B8731C59B141}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46B53894-94FD-41DF-C7CC-A3623B8B0804}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6581,22 +8931,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>309562</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>83287</xdr:rowOff>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FAFDBAD-D542-941A-D454-45482BCE7611}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2FCDC96-0381-AB8B-AACD-B8731C59B141}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6616,23 +8966,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>604837</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>300037</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>169012</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>309562</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>83287</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C455B32-1B7E-55D4-704A-B32F59E6003A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FAFDBAD-D542-941A-D454-45482BCE7611}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6654,21 +9004,21 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>604837</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>300037</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>83287</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>169012</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF572F1B-0DB2-81AB-8B42-50F5481B68C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C455B32-1B7E-55D4-704A-B32F59E6003A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6688,23 +9038,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>604837</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>300037</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46B53894-94FD-41DF-C7CC-A3623B8B0804}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF572F1B-0DB2-81AB-8B42-50F5481B68C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6717,6 +9067,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355A6079-5CA6-59AA-5AD9-7197D886BAF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B43BEA24-3F84-0F0E-5AAC-AF3040BCAA24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7042,773 +9464,784 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A794442-7EDD-4B7F-9E93-0359649CCCF5}">
-  <dimension ref="A3:M40"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <f>L8</f>
+        <v>26.324399999999997</v>
+      </c>
+      <c r="C2" s="1">
+        <f>L14</f>
+        <v>133.3544</v>
+      </c>
+      <c r="D2" s="1">
+        <f>L20</f>
+        <v>13.138799999999998</v>
+      </c>
+      <c r="E2" s="1">
+        <f>L26</f>
+        <v>88.202000000000012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <f>L9</f>
+        <v>26.611700000000003</v>
+      </c>
+      <c r="C3" s="1">
+        <f>L15</f>
+        <v>50.8934</v>
+      </c>
+      <c r="D3" s="1">
+        <f>L21</f>
+        <v>35.071199999999997</v>
+      </c>
+      <c r="E3" s="1">
+        <f>L27</f>
+        <v>167.40899999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <f>L10</f>
+        <v>105.69579999999999</v>
+      </c>
+      <c r="C4" s="1">
+        <f>L16</f>
+        <v>763.62980000000005</v>
+      </c>
+      <c r="D4" s="1">
+        <f>L22</f>
+        <v>106.29249999999999</v>
+      </c>
+      <c r="E4" s="1">
+        <f>L28</f>
+        <v>671.24500000000012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1">
+        <v>7</v>
+      </c>
+      <c r="I7" s="1">
+        <v>8</v>
+      </c>
+      <c r="J7" s="1">
+        <v>9</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B8" s="1">
         <v>36</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C8" s="1">
+        <v>29.631</v>
+      </c>
+      <c r="D8">
+        <v>18.791</v>
+      </c>
+      <c r="E8" s="1">
+        <v>29.056999999999999</v>
+      </c>
+      <c r="F8" s="1">
+        <v>28.928999999999998</v>
+      </c>
+      <c r="G8" s="1">
+        <v>18.428000000000001</v>
+      </c>
+      <c r="H8" s="1">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="I8" s="2">
+        <v>27.306000000000001</v>
+      </c>
+      <c r="J8" s="2">
+        <v>27.988</v>
+      </c>
+      <c r="K8" s="2">
+        <v>29.693999999999999</v>
+      </c>
+      <c r="L8" s="1">
+        <f>AVERAGE(B8:K8)</f>
+        <v>26.324399999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1">
+        <v>26.058</v>
+      </c>
+      <c r="D9" s="1">
+        <v>24.521000000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>25.393999999999998</v>
+      </c>
+      <c r="F9" s="1">
+        <v>24.667999999999999</v>
+      </c>
+      <c r="G9" s="1">
+        <v>25.027000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>24.248000000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>27.858000000000001</v>
+      </c>
+      <c r="J9" s="1">
+        <v>25.13</v>
+      </c>
+      <c r="K9" s="1">
+        <v>24.213000000000001</v>
+      </c>
+      <c r="L9" s="1">
+        <f>AVERAGE(B9:K9)</f>
+        <v>26.611700000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1">
+        <v>68</v>
+      </c>
+      <c r="C10" s="1">
+        <v>140.102</v>
+      </c>
+      <c r="D10" s="1">
+        <v>42.460999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>89.234999999999999</v>
+      </c>
+      <c r="F10" s="1">
+        <v>142.15100000000001</v>
+      </c>
+      <c r="G10" s="1">
+        <v>177.51400000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>57.78</v>
+      </c>
+      <c r="I10" s="1">
+        <v>114.05800000000001</v>
+      </c>
+      <c r="J10" s="1">
+        <v>121.05200000000001</v>
+      </c>
+      <c r="K10" s="1">
+        <v>104.605</v>
+      </c>
+      <c r="L10" s="1">
+        <f>AVERAGE(B10:K10)</f>
+        <v>105.69579999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>6</v>
+      </c>
+      <c r="H13" s="1">
+        <v>7</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+      <c r="J13" s="1">
+        <v>9</v>
+      </c>
+      <c r="K13" s="1">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
         <v>183</v>
       </c>
-      <c r="D4" s="1">
-        <v>10.135999999999999</v>
-      </c>
-      <c r="E4" s="1">
-        <v>51.536999999999999</v>
-      </c>
-      <c r="F4" s="1">
-        <v>63.691000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1">
-        <v>75</v>
-      </c>
-      <c r="D5" s="1">
-        <v>29.62</v>
-      </c>
-      <c r="E5" s="1">
-        <v>147.721</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>68</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1041</v>
-      </c>
-      <c r="D6" s="1">
-        <v>97</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
-        <v>6</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7</v>
-      </c>
-      <c r="I10" s="1">
-        <v>8</v>
-      </c>
-      <c r="J10" s="1">
-        <v>9</v>
-      </c>
-      <c r="K10" s="1">
-        <v>10</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="F11" s="1">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="H11" s="1">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="K11" s="2">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="L11" s="1">
-        <f>AVERAGE(B11:K11)</f>
-        <v>8.6000000000000017E-3</v>
-      </c>
-      <c r="M11" s="2">
-        <v>7176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.153</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.161</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.218</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="L12" s="1">
-        <f>AVERAGE(B12:K12)</f>
-        <v>0.17409999999999998</v>
-      </c>
-      <c r="M12" s="1">
-        <v>7176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2.7E-2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D13" s="1">
-        <v>3.1E-2</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="H13" s="1">
-        <v>2.7E-2</v>
-      </c>
-      <c r="I13" s="1">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="J13" s="1">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="K13" s="1">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="L13" s="1">
-        <f>AVERAGE(B13:K13)</f>
-        <v>2.4199999999999999E-2</v>
-      </c>
-      <c r="M13" s="1">
-        <v>7176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.16</v>
-      </c>
       <c r="C14" s="1">
-        <v>0.182</v>
+        <v>147.54400000000001</v>
       </c>
       <c r="D14" s="1">
-        <v>0.17399999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="E14" s="1">
-        <v>0.19600000000000001</v>
+        <v>150.154</v>
       </c>
       <c r="F14" s="1">
-        <v>0.19</v>
+        <v>153.619</v>
       </c>
       <c r="G14" s="1">
-        <v>0.18</v>
+        <v>86.887</v>
       </c>
       <c r="H14" s="1">
-        <v>0.191</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0.16400000000000001</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0.18</v>
+        <v>85.766000000000005</v>
+      </c>
+      <c r="I14" s="2">
+        <v>147.97900000000001</v>
+      </c>
+      <c r="J14" s="2">
+        <v>146.07900000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <v>145.26599999999999</v>
       </c>
       <c r="L14" s="1">
         <f>AVERAGE(B14:K14)</f>
-        <v>0.18139999999999998</v>
-      </c>
-      <c r="M14" s="1">
-        <v>7176</v>
+        <v>133.3544</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1">
+        <v>75</v>
+      </c>
+      <c r="C15" s="1">
+        <v>47.259</v>
+      </c>
+      <c r="D15" s="1">
+        <v>47.514000000000003</v>
+      </c>
+      <c r="E15" s="1">
+        <v>48.078000000000003</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45.253</v>
+      </c>
+      <c r="G15" s="1">
+        <v>48.841000000000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>49.649000000000001</v>
+      </c>
+      <c r="I15" s="1">
+        <v>51.773000000000003</v>
+      </c>
+      <c r="J15" s="1">
+        <v>48.143000000000001</v>
+      </c>
+      <c r="K15" s="1">
+        <v>47.423999999999999</v>
+      </c>
+      <c r="L15" s="1">
+        <f>AVERAGE(B15:K15)</f>
+        <v>50.8934</v>
+      </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="1">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1">
-        <v>4</v>
-      </c>
-      <c r="F17" s="1">
-        <v>5</v>
-      </c>
-      <c r="G17" s="1">
-        <v>6</v>
-      </c>
-      <c r="H17" s="1">
-        <v>7</v>
-      </c>
-      <c r="I17" s="1">
-        <v>8</v>
-      </c>
-      <c r="J17" s="1">
-        <v>9</v>
-      </c>
-      <c r="K17" s="1">
-        <v>10</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>18</v>
+      <c r="B16" s="1">
+        <v>1041</v>
+      </c>
+      <c r="C16" s="1">
+        <v>764.4</v>
+      </c>
+      <c r="D16" s="1">
+        <v>616.178</v>
+      </c>
+      <c r="E16" s="1">
+        <v>766.34900000000005</v>
+      </c>
+      <c r="F16" s="1">
+        <v>755.65800000000002</v>
+      </c>
+      <c r="G16" s="1">
+        <v>757.596</v>
+      </c>
+      <c r="H16" s="1">
+        <v>748.79600000000005</v>
+      </c>
+      <c r="I16" s="1">
+        <v>740.07100000000003</v>
+      </c>
+      <c r="J16" s="1">
+        <v>743.64</v>
+      </c>
+      <c r="K16" s="1">
+        <v>702.61</v>
+      </c>
+      <c r="L16" s="1">
+        <f>AVERAGE(B16:K16)</f>
+        <v>763.62980000000005</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0.247</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.23100000000000001</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0.32700000000000001</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0.23200000000000001</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="L18" s="1">
-        <f>AVERAGE(B18:K18)</f>
-        <v>0.251</v>
-      </c>
-      <c r="M18" s="1">
-        <v>240949</v>
-      </c>
+      <c r="B18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
         <v>4</v>
       </c>
-      <c r="B19" s="1">
-        <v>9.6039999999999992</v>
-      </c>
-      <c r="C19" s="1">
-        <v>6.3339999999999996</v>
-      </c>
-      <c r="D19" s="1">
-        <v>6.1139999999999999</v>
-      </c>
-      <c r="E19" s="1">
-        <v>6.1120000000000001</v>
-      </c>
       <c r="F19" s="1">
-        <v>6.2460000000000004</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>6.306</v>
+        <v>6</v>
       </c>
       <c r="H19" s="1">
-        <v>6.3019999999999996</v>
+        <v>7</v>
       </c>
       <c r="I19" s="1">
-        <v>12.12</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1">
-        <v>5.859</v>
+        <v>9</v>
       </c>
       <c r="K19" s="1">
-        <v>5.6890000000000001</v>
-      </c>
-      <c r="L19" s="1">
-        <f>AVERAGE(B19:K19)</f>
-        <v>7.0686000000000009</v>
-      </c>
-      <c r="M19" s="1">
-        <v>240949</v>
+        <v>10</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B20" s="1">
-        <v>5.2859999999999996</v>
+        <v>10.135999999999999</v>
       </c>
       <c r="C20" s="1">
-        <v>5.7279999999999998</v>
+        <v>15.295999999999999</v>
       </c>
       <c r="D20" s="1">
-        <v>5.4749999999999996</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="E20" s="1">
-        <v>5.5940000000000003</v>
+        <v>14.686</v>
       </c>
       <c r="F20" s="1">
-        <v>5.1379999999999999</v>
+        <v>15.606</v>
       </c>
       <c r="G20" s="1">
-        <v>5.0979999999999999</v>
+        <v>9.6170000000000009</v>
       </c>
       <c r="H20" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="I20" s="1">
-        <v>5.0629999999999997</v>
-      </c>
-      <c r="J20" s="1">
-        <v>5.5659999999999998</v>
-      </c>
-      <c r="K20" s="1">
-        <v>5.7160000000000002</v>
+        <v>9.7370000000000001</v>
+      </c>
+      <c r="I20" s="2">
+        <v>15.529</v>
+      </c>
+      <c r="J20" s="2">
+        <v>14.917999999999999</v>
+      </c>
+      <c r="K20" s="2">
+        <v>16.606000000000002</v>
       </c>
       <c r="L20" s="1">
         <f>AVERAGE(B20:K20)</f>
-        <v>5.3864000000000001</v>
-      </c>
-      <c r="M20" s="1">
-        <v>240949</v>
+        <v>13.138799999999998</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B21" s="1">
-        <v>6.2539999999999996</v>
+        <v>29.62</v>
       </c>
       <c r="C21" s="1">
-        <v>7.0019999999999998</v>
+        <v>35.389000000000003</v>
       </c>
       <c r="D21" s="1">
-        <v>6.9569999999999999</v>
+        <v>38.695</v>
       </c>
       <c r="E21" s="1">
-        <v>7.048</v>
+        <v>34.912999999999997</v>
       </c>
       <c r="F21" s="1">
-        <v>6.8529999999999998</v>
+        <v>38.325000000000003</v>
       </c>
       <c r="G21" s="1">
-        <v>7.1289999999999996</v>
+        <v>33.274999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>6.702</v>
+        <v>35.993000000000002</v>
       </c>
       <c r="I21" s="1">
-        <v>6.4059999999999997</v>
+        <v>33.753999999999998</v>
       </c>
       <c r="J21" s="1">
-        <v>6.6239999999999997</v>
+        <v>36.777999999999999</v>
       </c>
       <c r="K21" s="1">
-        <v>6.4660000000000002</v>
+        <v>33.97</v>
       </c>
       <c r="L21" s="1">
         <f>AVERAGE(B21:K21)</f>
-        <v>6.7441000000000004</v>
-      </c>
-      <c r="M21" s="1">
-        <v>240949</v>
+        <v>35.071199999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="1">
+        <v>97</v>
+      </c>
+      <c r="C22" s="1">
+        <v>104.125</v>
+      </c>
+      <c r="D22" s="1">
+        <v>80.650999999999996</v>
+      </c>
+      <c r="E22" s="1">
+        <v>89.963999999999999</v>
+      </c>
+      <c r="F22" s="1">
+        <v>126.736</v>
+      </c>
+      <c r="G22" s="1">
+        <v>87.064999999999998</v>
+      </c>
+      <c r="H22" s="1">
+        <v>120.006</v>
+      </c>
+      <c r="I22" s="1">
+        <v>120.53400000000001</v>
+      </c>
+      <c r="J22" s="1">
+        <v>121.527</v>
+      </c>
+      <c r="K22" s="1">
+        <v>115.31699999999999</v>
+      </c>
+      <c r="L22" s="1">
+        <f>AVERAGE(B22:K22)</f>
+        <v>106.29249999999999</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1">
-        <v>2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>4</v>
-      </c>
-      <c r="F24" s="1">
-        <v>5</v>
-      </c>
-      <c r="G24" s="1">
-        <v>6</v>
-      </c>
-      <c r="H24" s="1">
-        <v>7</v>
-      </c>
-      <c r="I24" s="1">
-        <v>8</v>
-      </c>
-      <c r="J24" s="1">
-        <v>9</v>
-      </c>
-      <c r="K24" s="1">
-        <v>10</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="B24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1">
         <v>3</v>
       </c>
-      <c r="B25" s="1">
-        <v>1.635</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1.5609999999999999</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1.593</v>
-      </c>
       <c r="E25" s="1">
-        <v>1.5249999999999999</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1">
-        <v>1.484</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>1.4910000000000001</v>
+        <v>6</v>
       </c>
       <c r="H25" s="1">
-        <v>1.4350000000000001</v>
+        <v>7</v>
       </c>
       <c r="I25" s="1">
-        <v>1.6739999999999999</v>
+        <v>8</v>
       </c>
       <c r="J25" s="1">
-        <v>1.552</v>
+        <v>9</v>
       </c>
       <c r="K25" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="L25" s="1">
-        <f>AVERAGE(B25:K25)</f>
-        <v>1.552</v>
-      </c>
-      <c r="M25" s="1">
-        <v>814122</v>
+        <v>10</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B26" s="1">
-        <v>50.73</v>
+        <v>51.536999999999999</v>
       </c>
       <c r="C26" s="1">
-        <v>25.795000000000002</v>
+        <v>108.20399999999999</v>
       </c>
       <c r="D26" s="1">
-        <v>33.256</v>
+        <v>62.531999999999996</v>
       </c>
       <c r="E26" s="1">
-        <v>24.081</v>
+        <v>108.259</v>
       </c>
       <c r="F26" s="1">
-        <v>24.37</v>
+        <v>110.886</v>
       </c>
       <c r="G26" s="1">
-        <v>26.594000000000001</v>
+        <v>63.735999999999997</v>
       </c>
       <c r="H26" s="1">
-        <v>24.925999999999998</v>
-      </c>
-      <c r="I26" s="1">
-        <v>24.792000000000002</v>
-      </c>
-      <c r="J26" s="1">
-        <v>23.780999999999999</v>
-      </c>
-      <c r="K26" s="1">
-        <v>25.387</v>
+        <v>62.685000000000002</v>
+      </c>
+      <c r="I26" s="2">
+        <v>104.099</v>
+      </c>
+      <c r="J26" s="2">
+        <v>100.56</v>
+      </c>
+      <c r="K26" s="2">
+        <v>109.52200000000001</v>
       </c>
       <c r="L26" s="1">
         <f>AVERAGE(B26:K26)</f>
-        <v>28.371199999999998</v>
-      </c>
-      <c r="M26" s="1">
-        <v>814122</v>
+        <v>88.202000000000012</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B27" s="1">
-        <v>33.542000000000002</v>
-      </c>
-      <c r="C27" s="1">
-        <v>34.146999999999998</v>
+        <v>147.721</v>
+      </c>
+      <c r="C27" s="9">
+        <v>158.97300000000001</v>
       </c>
       <c r="D27" s="1">
-        <v>34.21</v>
+        <v>165.31800000000001</v>
       </c>
       <c r="E27" s="1">
-        <v>33.317999999999998</v>
+        <v>195.46299999999999</v>
       </c>
       <c r="F27" s="1">
-        <v>35.713000000000001</v>
+        <v>168.44900000000001</v>
       </c>
       <c r="G27" s="1">
-        <v>36.479999999999997</v>
+        <v>168.05799999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>33.959000000000003</v>
+        <v>172.678</v>
       </c>
       <c r="I27" s="1">
-        <v>33.459000000000003</v>
+        <v>177.273</v>
       </c>
       <c r="J27" s="1">
-        <v>34.555</v>
+        <v>174.452</v>
       </c>
       <c r="K27" s="1">
-        <v>34.398000000000003</v>
+        <v>145.70500000000001</v>
       </c>
       <c r="L27" s="1">
         <f>AVERAGE(B27:K27)</f>
-        <v>34.378100000000003</v>
-      </c>
-      <c r="M27" s="1">
-        <v>814122</v>
+        <v>167.40899999999996</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B28" s="1">
-        <v>50.683</v>
+        <v>1159</v>
       </c>
       <c r="C28" s="1">
-        <v>53.917999999999999</v>
+        <v>676.85299999999995</v>
       </c>
       <c r="D28" s="1">
-        <v>51.317</v>
+        <v>472.33600000000001</v>
       </c>
       <c r="E28" s="1">
-        <v>50.415999999999997</v>
+        <v>490.07400000000001</v>
       </c>
       <c r="F28" s="1">
-        <v>50.917999999999999</v>
+        <v>740.62699999999995</v>
       </c>
       <c r="G28" s="1">
-        <v>50.692999999999998</v>
+        <v>512.08500000000004</v>
       </c>
       <c r="H28" s="1">
-        <v>50.76</v>
+        <v>667.59</v>
       </c>
       <c r="I28" s="1">
-        <v>50.936</v>
+        <v>665.35799999999995</v>
       </c>
       <c r="J28" s="1">
-        <v>50.365000000000002</v>
+        <v>665.87</v>
       </c>
       <c r="K28" s="1">
-        <v>52.921999999999997</v>
+        <v>662.65700000000004</v>
       </c>
       <c r="L28" s="1">
         <f>AVERAGE(B28:K28)</f>
-        <v>51.2928</v>
-      </c>
-      <c r="M28" s="1">
-        <v>814122</v>
+        <v>671.24500000000012</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="B30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -7848,7 +10281,7 @@
         <v>8</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -7856,41 +10289,41 @@
         <v>3</v>
       </c>
       <c r="B32" s="1">
-        <v>2.306</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C32" s="1">
-        <v>2.6320000000000001</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D32" s="1">
-        <v>2.2829999999999999</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E32" s="1">
-        <v>2.4329999999999998</v>
+        <v>0.03</v>
       </c>
       <c r="F32" s="1">
-        <v>2.3530000000000002</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="G32" s="1">
-        <v>2.3959999999999999</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H32" s="1">
-        <v>2.2490000000000001</v>
-      </c>
-      <c r="I32" s="1">
-        <v>2.5659999999999998</v>
-      </c>
-      <c r="J32" s="1">
-        <v>2.5529999999999999</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2.4449999999999998</v>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J32" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K32" s="2">
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="L32" s="1">
         <f>AVERAGE(B32:K32)</f>
-        <v>2.4215999999999998</v>
-      </c>
-      <c r="M32" s="1">
-        <v>1051030</v>
+        <v>8.6000000000000017E-3</v>
+      </c>
+      <c r="M32" s="2">
+        <v>7176</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -7898,41 +10331,41 @@
         <v>4</v>
       </c>
       <c r="B33" s="1">
-        <v>84.95</v>
+        <v>0.15</v>
       </c>
       <c r="C33" s="1">
-        <v>19.603999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="D33" s="1">
-        <v>20.89</v>
+        <v>0.161</v>
       </c>
       <c r="E33" s="1">
-        <v>17.632000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="F33" s="1">
-        <v>17.361999999999998</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="G33" s="1">
-        <v>18.946000000000002</v>
+        <v>0.218</v>
       </c>
       <c r="H33" s="1">
-        <v>18.132000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="I33" s="1">
-        <v>19.100999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="J33" s="1">
-        <v>17.574999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="K33" s="1">
-        <v>18.085999999999999</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="L33" s="1">
         <f>AVERAGE(B33:K33)</f>
-        <v>25.227799999999995</v>
+        <v>0.17409999999999998</v>
       </c>
       <c r="M33" s="1">
-        <v>1051030</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -7940,41 +10373,41 @@
         <v>5</v>
       </c>
       <c r="B34" s="1">
-        <v>84.057000000000002</v>
+        <v>2.7E-2</v>
       </c>
       <c r="C34" s="1">
-        <v>83.819000000000003</v>
+        <v>0.02</v>
       </c>
       <c r="D34" s="1">
-        <v>87.9</v>
+        <v>3.1E-2</v>
       </c>
       <c r="E34" s="1">
-        <v>83.581999999999994</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F34" s="1">
-        <v>79.046000000000006</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G34" s="1">
-        <v>69.576999999999998</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H34" s="1">
-        <v>79.350999999999999</v>
+        <v>2.7E-2</v>
       </c>
       <c r="I34" s="1">
-        <v>76.429000000000002</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="J34" s="1">
-        <v>77.981999999999999</v>
-      </c>
-      <c r="K34" s="4">
-        <v>82.072999999999993</v>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="K34" s="1">
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="L34" s="1">
         <f>AVERAGE(B34:K34)</f>
-        <v>80.381599999999992</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="M34" s="1">
-        <v>1051030</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -7982,108 +10415,1264 @@
         <v>6</v>
       </c>
       <c r="B35" s="1">
-        <v>72.956999999999994</v>
+        <v>0.16</v>
       </c>
       <c r="C35" s="1">
-        <v>74.742999999999995</v>
+        <v>0.182</v>
       </c>
       <c r="D35" s="1">
-        <v>78.183000000000007</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="E35" s="1">
-        <v>73.454999999999998</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F35" s="1">
-        <v>70.302999999999997</v>
+        <v>0.19</v>
       </c>
       <c r="G35" s="1">
-        <v>71.822000000000003</v>
+        <v>0.18</v>
       </c>
       <c r="H35" s="1">
-        <v>71.528999999999996</v>
+        <v>0.191</v>
       </c>
       <c r="I35" s="1">
-        <v>72.44</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="J35" s="1">
-        <v>70.861999999999995</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="K35" s="1">
-        <v>72.620999999999995</v>
+        <v>0.18</v>
       </c>
       <c r="L35" s="1">
         <f>AVERAGE(B35:K35)</f>
-        <v>72.891499999999994</v>
+        <v>0.18139999999999998</v>
       </c>
       <c r="M35" s="1">
-        <v>1051030</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>19</v>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1">
+        <v>4</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>6</v>
+      </c>
+      <c r="H38" s="1">
+        <v>7</v>
+      </c>
+      <c r="I38" s="1">
+        <v>8</v>
+      </c>
+      <c r="J38" s="1">
+        <v>9</v>
+      </c>
+      <c r="K38" s="1">
         <v>10</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="L38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="A39" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.247</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="L39" s="1">
+        <f>AVERAGE(B39:K39)</f>
+        <v>0.251</v>
+      </c>
+      <c r="M39" s="1">
+        <v>240949</v>
+      </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1">
+        <v>9.6039999999999992</v>
+      </c>
+      <c r="C40" s="1">
+        <v>6.3339999999999996</v>
+      </c>
+      <c r="D40" s="1">
+        <v>6.1139999999999999</v>
+      </c>
+      <c r="E40" s="1">
+        <v>6.1120000000000001</v>
+      </c>
+      <c r="F40" s="1">
+        <v>6.2460000000000004</v>
+      </c>
+      <c r="G40" s="1">
+        <v>6.306</v>
+      </c>
+      <c r="H40" s="1">
+        <v>6.3019999999999996</v>
+      </c>
+      <c r="I40" s="1">
+        <v>12.12</v>
+      </c>
+      <c r="J40" s="1">
+        <v>5.859</v>
+      </c>
+      <c r="K40" s="1">
+        <v>5.6890000000000001</v>
+      </c>
+      <c r="L40" s="1">
+        <f>AVERAGE(B40:K40)</f>
+        <v>7.0686000000000009</v>
+      </c>
+      <c r="M40" s="1">
+        <v>240949</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="1">
+        <v>5.2859999999999996</v>
+      </c>
+      <c r="C41" s="1">
+        <v>5.7279999999999998</v>
+      </c>
+      <c r="D41" s="1">
+        <v>5.4749999999999996</v>
+      </c>
+      <c r="E41" s="1">
+        <v>5.5940000000000003</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5.1379999999999999</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5.0979999999999999</v>
+      </c>
+      <c r="H41" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5.0629999999999997</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="K41" s="1">
+        <v>5.7160000000000002</v>
+      </c>
+      <c r="L41" s="1">
+        <f>AVERAGE(B41:K41)</f>
+        <v>5.3864000000000001</v>
+      </c>
+      <c r="M41" s="1">
+        <v>240949</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="1">
+        <v>6.2539999999999996</v>
+      </c>
+      <c r="C42" s="1">
+        <v>7.0019999999999998</v>
+      </c>
+      <c r="D42" s="1">
+        <v>6.9569999999999999</v>
+      </c>
+      <c r="E42" s="1">
+        <v>7.048</v>
+      </c>
+      <c r="F42" s="1">
+        <v>6.8529999999999998</v>
+      </c>
+      <c r="G42" s="1">
+        <v>7.1289999999999996</v>
+      </c>
+      <c r="H42" s="1">
+        <v>6.702</v>
+      </c>
+      <c r="I42" s="1">
+        <v>6.4059999999999997</v>
+      </c>
+      <c r="J42" s="1">
+        <v>6.6239999999999997</v>
+      </c>
+      <c r="K42" s="1">
+        <v>6.4660000000000002</v>
+      </c>
+      <c r="L42" s="1">
+        <f>AVERAGE(B42:K42)</f>
+        <v>6.7441000000000004</v>
+      </c>
+      <c r="M42" s="1">
+        <v>240949</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>4</v>
+      </c>
+      <c r="F45" s="1">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1">
+        <v>6</v>
+      </c>
+      <c r="H45" s="1">
+        <v>7</v>
+      </c>
+      <c r="I45" s="1">
+        <v>8</v>
+      </c>
+      <c r="J45" s="1">
+        <v>9</v>
+      </c>
+      <c r="K45" s="1">
+        <v>10</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1.635</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1.5609999999999999</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1.593</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1.484</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1.4910000000000001</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1.6739999999999999</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1.552</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="L46" s="1">
+        <f>AVERAGE(B46:K46)</f>
+        <v>1.552</v>
+      </c>
+      <c r="M46" s="1">
+        <v>814122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1">
+        <v>50.73</v>
+      </c>
+      <c r="C47" s="1">
+        <v>25.795000000000002</v>
+      </c>
+      <c r="D47" s="1">
+        <v>33.256</v>
+      </c>
+      <c r="E47" s="1">
+        <v>24.081</v>
+      </c>
+      <c r="F47" s="1">
+        <v>24.37</v>
+      </c>
+      <c r="G47" s="1">
+        <v>26.594000000000001</v>
+      </c>
+      <c r="H47" s="1">
+        <v>24.925999999999998</v>
+      </c>
+      <c r="I47" s="1">
+        <v>24.792000000000002</v>
+      </c>
+      <c r="J47" s="1">
+        <v>23.780999999999999</v>
+      </c>
+      <c r="K47" s="1">
+        <v>25.387</v>
+      </c>
+      <c r="L47" s="1">
+        <f>AVERAGE(B47:K47)</f>
+        <v>28.371199999999998</v>
+      </c>
+      <c r="M47" s="1">
+        <v>814122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="1">
+        <v>33.542000000000002</v>
+      </c>
+      <c r="C48" s="1">
+        <v>34.146999999999998</v>
+      </c>
+      <c r="D48" s="1">
+        <v>34.21</v>
+      </c>
+      <c r="E48" s="1">
+        <v>33.317999999999998</v>
+      </c>
+      <c r="F48" s="1">
+        <v>35.713000000000001</v>
+      </c>
+      <c r="G48" s="1">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="H48" s="1">
+        <v>33.959000000000003</v>
+      </c>
+      <c r="I48" s="1">
+        <v>33.459000000000003</v>
+      </c>
+      <c r="J48" s="1">
+        <v>34.555</v>
+      </c>
+      <c r="K48" s="1">
+        <v>34.398000000000003</v>
+      </c>
+      <c r="L48" s="1">
+        <f>AVERAGE(B48:K48)</f>
+        <v>34.378100000000003</v>
+      </c>
+      <c r="M48" s="1">
+        <v>814122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="1">
+        <v>50.683</v>
+      </c>
+      <c r="C49" s="1">
+        <v>53.917999999999999</v>
+      </c>
+      <c r="D49" s="1">
+        <v>51.317</v>
+      </c>
+      <c r="E49" s="1">
+        <v>50.415999999999997</v>
+      </c>
+      <c r="F49" s="1">
+        <v>50.917999999999999</v>
+      </c>
+      <c r="G49" s="1">
+        <v>50.692999999999998</v>
+      </c>
+      <c r="H49" s="1">
+        <v>50.76</v>
+      </c>
+      <c r="I49" s="1">
+        <v>50.936</v>
+      </c>
+      <c r="J49" s="1">
+        <v>50.365000000000002</v>
+      </c>
+      <c r="K49" s="1">
+        <v>52.921999999999997</v>
+      </c>
+      <c r="L49" s="1">
+        <f>AVERAGE(B49:K49)</f>
+        <v>51.2928</v>
+      </c>
+      <c r="M49" s="1">
+        <v>814122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5</v>
+      </c>
+      <c r="G52" s="1">
+        <v>6</v>
+      </c>
+      <c r="H52" s="1">
+        <v>7</v>
+      </c>
+      <c r="I52" s="1">
+        <v>8</v>
+      </c>
+      <c r="J52" s="1">
+        <v>9</v>
+      </c>
+      <c r="K52" s="1">
+        <v>10</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2.306</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.6320000000000001</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2.2829999999999999</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2.4329999999999998</v>
+      </c>
+      <c r="F53" s="1">
+        <v>2.3530000000000002</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2.3959999999999999</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="I53" s="1">
+        <v>2.5659999999999998</v>
+      </c>
+      <c r="J53" s="1">
+        <v>2.5529999999999999</v>
+      </c>
+      <c r="K53" s="1">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="L53" s="1">
+        <f>AVERAGE(B53:K53)</f>
+        <v>2.4215999999999998</v>
+      </c>
+      <c r="M53" s="1">
+        <v>1051030</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="1">
+        <v>84.95</v>
+      </c>
+      <c r="C54" s="1">
+        <v>19.603999999999999</v>
+      </c>
+      <c r="D54" s="1">
+        <v>20.89</v>
+      </c>
+      <c r="E54" s="1">
+        <v>17.632000000000001</v>
+      </c>
+      <c r="F54" s="1">
+        <v>17.361999999999998</v>
+      </c>
+      <c r="G54" s="1">
+        <v>18.946000000000002</v>
+      </c>
+      <c r="H54" s="1">
+        <v>18.132000000000001</v>
+      </c>
+      <c r="I54" s="1">
+        <v>19.100999999999999</v>
+      </c>
+      <c r="J54" s="1">
+        <v>17.574999999999999</v>
+      </c>
+      <c r="K54" s="1">
+        <v>18.085999999999999</v>
+      </c>
+      <c r="L54" s="1">
+        <f>AVERAGE(B54:K54)</f>
+        <v>25.227799999999995</v>
+      </c>
+      <c r="M54" s="1">
+        <v>1051030</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="1">
+        <v>84.057000000000002</v>
+      </c>
+      <c r="C55" s="1">
+        <v>83.819000000000003</v>
+      </c>
+      <c r="D55" s="1">
+        <v>87.9</v>
+      </c>
+      <c r="E55" s="1">
+        <v>83.581999999999994</v>
+      </c>
+      <c r="F55" s="1">
+        <v>79.046000000000006</v>
+      </c>
+      <c r="G55" s="1">
+        <v>69.576999999999998</v>
+      </c>
+      <c r="H55" s="1">
+        <v>79.350999999999999</v>
+      </c>
+      <c r="I55" s="1">
+        <v>76.429000000000002</v>
+      </c>
+      <c r="J55" s="1">
+        <v>77.981999999999999</v>
+      </c>
+      <c r="K55" s="4">
+        <v>82.072999999999993</v>
+      </c>
+      <c r="L55" s="1">
+        <f>AVERAGE(B55:K55)</f>
+        <v>80.381599999999992</v>
+      </c>
+      <c r="M55" s="1">
+        <v>1051030</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="1">
+        <v>72.956999999999994</v>
+      </c>
+      <c r="C56" s="1">
+        <v>74.742999999999995</v>
+      </c>
+      <c r="D56" s="1">
+        <v>78.183000000000007</v>
+      </c>
+      <c r="E56" s="1">
+        <v>73.454999999999998</v>
+      </c>
+      <c r="F56" s="1">
+        <v>70.302999999999997</v>
+      </c>
+      <c r="G56" s="1">
+        <v>71.822000000000003</v>
+      </c>
+      <c r="H56" s="1">
+        <v>71.528999999999996</v>
+      </c>
+      <c r="I56" s="1">
+        <v>72.44</v>
+      </c>
+      <c r="J56" s="1">
+        <v>70.861999999999995</v>
+      </c>
+      <c r="K56" s="1">
+        <v>72.620999999999995</v>
+      </c>
+      <c r="L56" s="1">
+        <f>AVERAGE(B56:K56)</f>
+        <v>72.891499999999994</v>
+      </c>
+      <c r="M56" s="1">
+        <v>1051030</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B58" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1">
+        <v>5</v>
+      </c>
+      <c r="G59" s="1">
+        <v>6</v>
+      </c>
+      <c r="H59" s="1">
+        <v>7</v>
+      </c>
+      <c r="I59" s="1">
+        <v>8</v>
+      </c>
+      <c r="J59" s="1">
+        <v>9</v>
+      </c>
+      <c r="K59" s="1">
+        <v>10</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="1">
+        <v>6.3E-2</v>
+      </c>
+      <c r="C60" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D60" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="H60" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I60" s="1">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K60" s="1">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L60" s="1">
+        <f>AVERAGE(B60:K60)</f>
+        <v>1.3600000000000004E-2</v>
+      </c>
+      <c r="M60" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="F61" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="H61" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="L61" s="1">
+        <f>AVERAGE(B61:K61)</f>
+        <v>1.7000000000000001E-3</v>
+      </c>
+      <c r="M61" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0.217</v>
+      </c>
+      <c r="C62" s="1">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.106</v>
+      </c>
+      <c r="E62" s="1">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H62" s="1">
+        <v>7.8E-2</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="J62" s="1">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="K62" s="4">
+        <v>0.113</v>
+      </c>
+      <c r="L62" s="1">
+        <f>AVERAGE(B62:K62)</f>
+        <v>0.10629999999999999</v>
+      </c>
+      <c r="M62" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C63" s="1">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="F63" s="1">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="G63" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="H63" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J63" s="1">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="L63" s="1">
+        <f>AVERAGE(B63:K63)</f>
+        <v>3.5199999999999995E-2</v>
+      </c>
+      <c r="M63" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+      <c r="M65" s="7"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="1">
+        <v>1</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1">
+        <v>4</v>
+      </c>
+      <c r="F66" s="1">
+        <v>5</v>
+      </c>
+      <c r="G66" s="1">
+        <v>6</v>
+      </c>
+      <c r="H66" s="1">
+        <v>7</v>
+      </c>
+      <c r="I66" s="1">
+        <v>8</v>
+      </c>
+      <c r="J66" s="1">
+        <v>9</v>
+      </c>
+      <c r="K66" s="1">
+        <v>10</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="1">
+        <v>4.7E-2</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="J67" s="1">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="K67" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="L67" s="1">
+        <f>AVERAGE(B67:K67)</f>
+        <v>1.7499999999999998E-2</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1" t="e">
+        <f>AVERAGE(B68:K68)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="1" t="e">
+        <f>AVERAGE(B69:K69)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2.0569999999999999</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1.88</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1.6779999999999999</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1.7909999999999999</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.9930000000000001</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1.9339999999999999</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1.7889999999999999</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1.7649999999999999</v>
+      </c>
+      <c r="L70" s="1">
+        <f>AVERAGE(B70:K70)</f>
+        <v>1.8509</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
+  <mergeCells count="16">
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="B78:M78"/>
     <mergeCell ref="B30:M30"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B51:M51"/>
+    <mergeCell ref="B44:M44"/>
+    <mergeCell ref="B37:M37"/>
+    <mergeCell ref="B73:M73"/>
+    <mergeCell ref="B74:M74"/>
+    <mergeCell ref="B75:M75"/>
+    <mergeCell ref="B76:M76"/>
+    <mergeCell ref="B77:M77"/>
+    <mergeCell ref="B58:M58"/>
+    <mergeCell ref="B65:M65"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Measurement.xlsx
+++ b/Measurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gajaj\Desktop\School\Bachelor\graph_databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078C74EB-3859-4BEF-AF93-C143EAB8A83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00636F2F-3E27-441A-BB74-2ECF7B9FBB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="33">
   <si>
     <t>Neo4j</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>delete Edges</t>
+  </si>
+  <si>
+    <t>hran = 3</t>
   </si>
 </sst>
 </file>
@@ -254,13 +257,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -270,7 +274,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,16 +508,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>105.69579999999999</c:v>
+                  <c:v>110.23260000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>763.62980000000005</c:v>
+                  <c:v>731.18219999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>106.29249999999999</c:v>
+                  <c:v>108.37280000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>671.24500000000012</c:v>
+                  <c:v>614.11620000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1830,34 +1836,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>5.2859999999999996</c:v>
+                  <c:v>3.1379999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.7279999999999998</c:v>
+                  <c:v>2.8980000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.4749999999999996</c:v>
+                  <c:v>3.0550000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.5940000000000003</c:v>
+                  <c:v>2.7280000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1379999999999999</c:v>
+                  <c:v>5.3250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.0979999999999999</c:v>
+                  <c:v>3.22</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.2</c:v>
+                  <c:v>3.9620000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.0629999999999997</c:v>
+                  <c:v>3.7509999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.5659999999999998</c:v>
+                  <c:v>3.9319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.7160000000000002</c:v>
+                  <c:v>3.8039999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4065,34 +4071,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.05</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.6999999999999998E-2</c:v>
+                  <c:v>2.1000000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2000000000000001E-2</c:v>
+                  <c:v>2.3E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.03</c:v>
+                  <c:v>1.4999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.5999999999999997E-2</c:v>
+                  <c:v>1.7000000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3000000000000002E-2</c:v>
+                  <c:v>1.4999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.3000000000000002E-2</c:v>
+                  <c:v>1.2999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.5000000000000003E-2</c:v>
+                  <c:v>1.6E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.5999999999999997E-2</c:v>
+                  <c:v>1.7000000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.03</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4636,34 +4642,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.0569999999999999</c:v>
+                  <c:v>1.4570000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.88</c:v>
+                  <c:v>1.226</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.8109999999999999</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6779999999999999</c:v>
+                  <c:v>1.292</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.7909999999999999</c:v>
+                  <c:v>1.3180000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9930000000000001</c:v>
+                  <c:v>1.3109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.9339999999999999</c:v>
+                  <c:v>1.395</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.7889999999999999</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.8109999999999999</c:v>
+                  <c:v>1.343</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.7649999999999999</c:v>
+                  <c:v>1.256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8912,6 +8918,9 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46B53894-94FD-41DF-C7CC-A3623B8B0804}"/>
             </a:ext>
+            <a:ext uri="{C183D7F6-B498-43B3-948B-1728B52AA6E4}">
+              <adec:decorative xmlns:adec="http://schemas.microsoft.com/office/drawing/2017/decorative" val="0"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
@@ -9532,35 +9541,35 @@
       </c>
       <c r="B4" s="1">
         <f>L10</f>
-        <v>105.69579999999999</v>
+        <v>110.23260000000001</v>
       </c>
       <c r="C4" s="1">
         <f>L16</f>
-        <v>763.62980000000005</v>
+        <v>731.18219999999997</v>
       </c>
       <c r="D4" s="1">
         <f>L22</f>
-        <v>106.29249999999999</v>
+        <v>108.37280000000001</v>
       </c>
       <c r="E4" s="1">
         <f>L28</f>
-        <v>671.24500000000012</v>
+        <v>614.11620000000005</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -9683,7 +9692,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="1">
-        <v>68</v>
+        <v>113.36799999999999</v>
       </c>
       <c r="C10" s="1">
         <v>140.102</v>
@@ -9714,23 +9723,23 @@
       </c>
       <c r="L10" s="1">
         <f>AVERAGE(B10:K10)</f>
-        <v>105.69579999999999</v>
+        <v>110.23260000000001</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -9853,7 +9862,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="1">
-        <v>1041</v>
+        <v>716.524</v>
       </c>
       <c r="C16" s="1">
         <v>764.4</v>
@@ -9884,23 +9893,23 @@
       </c>
       <c r="L16" s="1">
         <f>AVERAGE(B16:K16)</f>
-        <v>763.62980000000005</v>
+        <v>731.18219999999997</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
@@ -10023,7 +10032,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="1">
-        <v>97</v>
+        <v>117.803</v>
       </c>
       <c r="C22" s="1">
         <v>104.125</v>
@@ -10054,23 +10063,23 @@
       </c>
       <c r="L22" s="1">
         <f>AVERAGE(B22:K22)</f>
-        <v>106.29249999999999</v>
+        <v>108.37280000000001</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -10156,7 +10165,7 @@
       <c r="B27" s="1">
         <v>147.721</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="6">
         <v>158.97300000000001</v>
       </c>
       <c r="D27" s="1">
@@ -10193,7 +10202,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="1">
-        <v>1159</v>
+        <v>587.71199999999999</v>
       </c>
       <c r="C28" s="1">
         <v>676.85299999999995</v>
@@ -10224,24 +10233,24 @@
       </c>
       <c r="L28" s="1">
         <f>AVERAGE(B28:K28)</f>
-        <v>671.24500000000012</v>
+        <v>614.11620000000005</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -10453,20 +10462,20 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
@@ -10598,38 +10607,38 @@
         <v>5</v>
       </c>
       <c r="B41" s="1">
-        <v>5.2859999999999996</v>
+        <v>3.1379999999999999</v>
       </c>
       <c r="C41" s="1">
-        <v>5.7279999999999998</v>
+        <v>2.8980000000000001</v>
       </c>
       <c r="D41" s="1">
-        <v>5.4749999999999996</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E41" s="1">
-        <v>5.5940000000000003</v>
+        <v>2.7280000000000002</v>
       </c>
       <c r="F41" s="1">
-        <v>5.1379999999999999</v>
+        <v>5.3250000000000002</v>
       </c>
       <c r="G41" s="1">
-        <v>5.0979999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="H41" s="1">
-        <v>5.2</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="I41" s="1">
-        <v>5.0629999999999997</v>
+        <v>3.7509999999999999</v>
       </c>
       <c r="J41" s="1">
-        <v>5.5659999999999998</v>
+        <v>3.9319999999999999</v>
       </c>
       <c r="K41" s="1">
-        <v>5.7160000000000002</v>
+        <v>3.8039999999999998</v>
       </c>
       <c r="L41" s="1">
         <f>AVERAGE(B41:K41)</f>
-        <v>5.3864000000000001</v>
+        <v>3.5813000000000001</v>
       </c>
       <c r="M41" s="1">
         <v>240949</v>
@@ -10678,20 +10687,20 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
@@ -10903,20 +10912,20 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -11128,20 +11137,20 @@
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
@@ -11222,8 +11231,8 @@
         <f>AVERAGE(B60:K60)</f>
         <v>1.3600000000000004E-2</v>
       </c>
-      <c r="M60" s="1">
-        <v>3</v>
+      <c r="M60" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -11264,8 +11273,8 @@
         <f>AVERAGE(B61:K61)</f>
         <v>1.7000000000000001E-3</v>
       </c>
-      <c r="M61" s="1">
-        <v>3</v>
+      <c r="M61" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -11306,8 +11315,8 @@
         <f>AVERAGE(B62:K62)</f>
         <v>0.10629999999999999</v>
       </c>
-      <c r="M62" s="1">
-        <v>3</v>
+      <c r="M62" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -11315,58 +11324,58 @@
         <v>6</v>
       </c>
       <c r="B63" s="1">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C63" s="1">
-        <v>3.6999999999999998E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="D63" s="1">
-        <v>3.2000000000000001E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="E63" s="1">
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F63" s="1">
-        <v>3.5999999999999997E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G63" s="1">
-        <v>3.3000000000000002E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H63" s="1">
-        <v>3.3000000000000002E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I63" s="1">
-        <v>3.5000000000000003E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="J63" s="1">
-        <v>3.5999999999999997E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="K63" s="1">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L63" s="1">
         <f>AVERAGE(B63:K63)</f>
-        <v>3.5199999999999995E-2</v>
-      </c>
-      <c r="M63" s="1">
-        <v>3</v>
+        <v>1.9700000000000002E-2</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
@@ -11500,38 +11509,38 @@
         <v>6</v>
       </c>
       <c r="B70" s="1">
-        <v>2.0569999999999999</v>
+        <v>1.4570000000000001</v>
       </c>
       <c r="C70" s="1">
-        <v>1.88</v>
+        <v>1.226</v>
       </c>
       <c r="D70" s="1">
-        <v>1.8109999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="E70" s="1">
-        <v>1.6779999999999999</v>
+        <v>1.292</v>
       </c>
       <c r="F70" s="1">
-        <v>1.7909999999999999</v>
+        <v>1.3180000000000001</v>
       </c>
       <c r="G70" s="1">
-        <v>1.9930000000000001</v>
+        <v>1.3109999999999999</v>
       </c>
       <c r="H70" s="1">
-        <v>1.9339999999999999</v>
+        <v>1.395</v>
       </c>
       <c r="I70" s="1">
-        <v>1.7889999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="J70" s="1">
-        <v>1.8109999999999999</v>
+        <v>1.343</v>
       </c>
       <c r="K70" s="1">
-        <v>1.7649999999999999</v>
+        <v>1.256</v>
       </c>
       <c r="L70" s="1">
         <f>AVERAGE(B70:K70)</f>
-        <v>1.8509</v>
+        <v>1.3097999999999999</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>25</v>
@@ -11541,115 +11550,115 @@
       <c r="A73" t="s">
         <v>7</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
+      <c r="M73" s="9"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="9"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>12</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="9"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>22</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>23</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Measurement.xlsx
+++ b/Measurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gajaj\Desktop\School\Bachelor\graph_databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7AE1AE-4117-4F48-AC1E-A4391000D945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC8BE79-F55F-4594-BECD-370B98866FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="3105" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
   </bookViews>
   <sheets>
     <sheet name="performance" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="39">
   <si>
     <t>Neo4j</t>
   </si>
@@ -145,9 +145,6 @@
     <t>SQL LE</t>
   </si>
   <si>
-    <t>zarazka</t>
-  </si>
-  <si>
     <t>Q7</t>
   </si>
   <si>
@@ -222,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -276,20 +273,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -300,19 +288,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -344,7 +329,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q1</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -1432,7 +1473,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q2</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -2297,7 +2394,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q4</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -3162,7 +3315,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q6</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -3805,7 +4014,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q5</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -5026,7 +5291,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q3</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -5891,7 +6212,63 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q7</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -6578,6 +6955,32 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>Q8</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6630,7 +7033,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6702,7 +7105,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6774,7 +7177,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6846,7 +7249,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -7116,37 +7519,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -12565,16 +12938,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12601,16 +12974,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>585787</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>319087</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>280987</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>113287</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12637,16 +13010,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>347662</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>309562</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>42862</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12673,16 +13046,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>75187</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>122812</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12709,16 +13082,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>157837</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12745,16 +13118,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>71436</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12786,16 +13159,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12822,16 +13195,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12864,15 +13237,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:colOff>600074</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13217,13 +13590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A794442-7EDD-4B7F-9E93-0359649CCCF5}">
-  <dimension ref="A1:AG55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -13263,11 +13636,11 @@
       <c r="M1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="8">
+      <c r="N1" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -13308,11 +13681,11 @@
       <c r="M2" s="2">
         <v>7176</v>
       </c>
-      <c r="N2" s="14">
+      <c r="N2" s="2">
         <v>0.06</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -13353,14 +13726,11 @@
       <c r="M3" s="1">
         <v>7176</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="1">
         <v>3.2480000000000002</v>
       </c>
-      <c r="AG3" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -13401,11 +13771,11 @@
       <c r="M4" s="1">
         <v>7176</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="1">
         <v>3.754</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -13446,11 +13816,11 @@
       <c r="M5" s="1">
         <v>7176</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="1">
         <v>3.04</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
@@ -13491,11 +13861,11 @@
       <c r="M6" s="1">
         <v>7176</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="1">
         <v>1.56</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>34</v>
       </c>
@@ -13536,11 +13906,11 @@
       <c r="M7" s="1">
         <v>7176</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="1">
         <v>1.0620000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -13580,11 +13950,11 @@
       <c r="M9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -13625,11 +13995,11 @@
       <c r="M10" s="1">
         <v>240949</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="2">
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -13670,11 +14040,11 @@
       <c r="M11" s="1">
         <v>240949</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="1">
         <v>7.1779999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -13715,11 +14085,11 @@
       <c r="M12" s="1">
         <v>240949</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="1">
         <v>9.2739999999999991</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -13760,11 +14130,11 @@
       <c r="M13" s="1">
         <v>240949</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="1">
         <v>6.165</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
@@ -13805,11 +14175,11 @@
       <c r="M14" s="1">
         <v>240949</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="1">
         <v>12.496</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>34</v>
       </c>
@@ -13850,7 +14220,7 @@
       <c r="M15" s="1">
         <v>240949</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="1">
         <v>11.238</v>
       </c>
     </row>
@@ -13894,6 +14264,9 @@
       <c r="M17" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -13936,7 +14309,7 @@
       <c r="M18" s="1">
         <v>814122</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="2">
         <v>1.645</v>
       </c>
     </row>
@@ -13981,7 +14354,7 @@
       <c r="M19" s="1">
         <v>814122</v>
       </c>
-      <c r="N19" s="4">
+      <c r="N19" s="1">
         <v>22.486000000000001</v>
       </c>
     </row>
@@ -14026,7 +14399,7 @@
       <c r="M20" s="1">
         <v>814122</v>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="1">
         <v>40.396999999999998</v>
       </c>
     </row>
@@ -14071,7 +14444,7 @@
       <c r="M21" s="1">
         <v>814122</v>
       </c>
-      <c r="N21" s="12">
+      <c r="N21" s="1">
         <v>28.344000000000001</v>
       </c>
     </row>
@@ -14116,7 +14489,7 @@
       <c r="M22" s="1">
         <v>814122</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="1">
         <v>85.111999999999995</v>
       </c>
     </row>
@@ -14161,7 +14534,7 @@
       <c r="M23" s="1">
         <v>814122</v>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="1">
         <v>51.231000000000002</v>
       </c>
     </row>
@@ -14205,6 +14578,9 @@
       <c r="M25" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -14247,7 +14623,7 @@
       <c r="M26" s="1">
         <v>1051030</v>
       </c>
-      <c r="N26" s="12">
+      <c r="N26" s="1">
         <v>2.5329999999999999</v>
       </c>
     </row>
@@ -14292,7 +14668,7 @@
       <c r="M27" s="1">
         <v>1051030</v>
       </c>
-      <c r="N27" s="4">
+      <c r="N27" s="1">
         <v>41.945</v>
       </c>
     </row>
@@ -14337,7 +14713,7 @@
       <c r="M28" s="1">
         <v>1051030</v>
       </c>
-      <c r="N28" s="12">
+      <c r="N28" s="1">
         <v>98.236999999999995</v>
       </c>
     </row>
@@ -14382,7 +14758,7 @@
       <c r="M29" s="1">
         <v>1051030</v>
       </c>
-      <c r="N29" s="12">
+      <c r="N29" s="1">
         <v>55.591999999999999</v>
       </c>
     </row>
@@ -14427,7 +14803,7 @@
       <c r="M30" s="1">
         <v>1051030</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="1">
         <v>94.417000000000002</v>
       </c>
     </row>
@@ -14472,7 +14848,7 @@
       <c r="M31" s="1">
         <v>1051030</v>
       </c>
-      <c r="N31" s="12">
+      <c r="N31" s="1">
         <v>73.567999999999998</v>
       </c>
     </row>
@@ -14516,6 +14892,9 @@
       <c r="M33" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
@@ -14558,7 +14937,7 @@
       <c r="M34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N34" s="1">
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
@@ -14603,7 +14982,7 @@
       <c r="M35" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="12">
+      <c r="N35" s="1">
         <v>1.2609999999999999</v>
       </c>
     </row>
@@ -14648,7 +15027,7 @@
       <c r="M36" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N36" s="12">
+      <c r="N36" s="1">
         <v>1.58</v>
       </c>
     </row>
@@ -14693,7 +15072,7 @@
       <c r="M37" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N37" s="12">
+      <c r="N37" s="1">
         <v>1.27</v>
       </c>
     </row>
@@ -14738,7 +15117,7 @@
       <c r="M38" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N38" s="13">
+      <c r="N38" s="1">
         <v>0.48599999999999999</v>
       </c>
     </row>
@@ -14783,7 +15162,7 @@
       <c r="M39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N39" s="12">
+      <c r="N39" s="1">
         <v>0.46899999999999997</v>
       </c>
     </row>
@@ -14827,6 +15206,9 @@
       <c r="M41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
@@ -14869,7 +15251,7 @@
       <c r="M42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N42" s="12">
+      <c r="N42" s="1">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -14894,6 +15276,7 @@
       <c r="M43" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
@@ -14916,6 +15299,7 @@
       <c r="M44" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
@@ -14933,6 +15317,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -14975,7 +15360,7 @@
       <c r="M46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N46" s="12">
+      <c r="N46" s="1">
         <v>2.4849999999999999</v>
       </c>
     </row>
@@ -15020,7 +15405,7 @@
       <c r="M47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N47" s="12">
+      <c r="N47" s="1">
         <v>2.2629999999999999</v>
       </c>
     </row>
@@ -15164,7 +15549,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="3">
         <v>1</v>
@@ -15250,7 +15635,7 @@
       <c r="N2" s="2">
         <v>0.33700000000000002</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="8">
         <v>0.34599999999999997</v>
       </c>
     </row>
@@ -15298,7 +15683,7 @@
       <c r="N3" s="1">
         <v>0.30399999999999999</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="4">
         <v>0.94399999999999995</v>
       </c>
     </row>
@@ -15346,7 +15731,7 @@
       <c r="N4" s="1">
         <v>4.0789999999999997</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="4">
         <v>7.1360000000000001</v>
       </c>
     </row>
@@ -15394,13 +15779,13 @@
       <c r="N5" s="1">
         <v>11.337999999999999</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="4">
         <v>9.3450000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -15486,7 +15871,7 @@
       <c r="N8" s="2">
         <v>0.222</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="8">
         <v>1.2789999999999999</v>
       </c>
     </row>
@@ -15534,7 +15919,7 @@
       <c r="N9" s="1">
         <v>0.378</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="4">
         <v>0.91300000000000003</v>
       </c>
     </row>
@@ -15582,7 +15967,7 @@
       <c r="N10" s="1">
         <v>4.0110000000000001</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="4">
         <v>8.125</v>
       </c>
     </row>
@@ -15630,16 +16015,16 @@
       <c r="N11" s="1">
         <v>5.2140000000000004</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="4">
         <v>7.4989999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -15655,10 +16040,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>

--- a/Measurement.xlsx
+++ b/Measurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gajaj\Desktop\School\Bachelor\graph_databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC8BE79-F55F-4594-BECD-370B98866FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C80513-498A-4B16-938E-867AC8ED3E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EE48DE2-4E6F-4460-AB34-FCF8C4BDCFE5}"/>
   </bookViews>
   <sheets>
     <sheet name="performance" sheetId="1" r:id="rId1"/>
@@ -277,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -288,7 +288,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -15413,115 +15412,115 @@
       <c r="A50" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>22</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -15541,13 +15540,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6E5F04-29EC-403B-9565-E01B10A010C8}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -15591,7 +15590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -15633,13 +15632,10 @@
         <v>13779</v>
       </c>
       <c r="N2" s="2">
-        <v>0.33700000000000002</v>
-      </c>
-      <c r="O2" s="8">
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -15681,13 +15677,10 @@
         <v>13779</v>
       </c>
       <c r="N3" s="1">
-        <v>0.30399999999999999</v>
-      </c>
-      <c r="O3" s="4">
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -15729,13 +15722,10 @@
         <v>13779</v>
       </c>
       <c r="N4" s="1">
-        <v>4.0789999999999997</v>
-      </c>
-      <c r="O4" s="4">
         <v>7.1360000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -15777,13 +15767,10 @@
         <v>13779</v>
       </c>
       <c r="N5" s="1">
-        <v>11.337999999999999</v>
-      </c>
-      <c r="O5" s="4">
         <v>9.3450000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -15827,7 +15814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -15869,13 +15856,10 @@
         <v>56.573999999999998</v>
       </c>
       <c r="N8" s="2">
-        <v>0.222</v>
-      </c>
-      <c r="O8" s="8">
         <v>1.2789999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -15917,13 +15901,10 @@
         <v>56.573999999999998</v>
       </c>
       <c r="N9" s="1">
-        <v>0.378</v>
-      </c>
-      <c r="O9" s="4">
         <v>0.91300000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -15965,13 +15946,10 @@
         <v>56.573999999999998</v>
       </c>
       <c r="N10" s="1">
-        <v>4.0110000000000001</v>
-      </c>
-      <c r="O10" s="4">
         <v>8.125</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
@@ -16013,49 +15991,46 @@
         <v>56.573999999999998</v>
       </c>
       <c r="N11" s="1">
-        <v>5.2140000000000004</v>
-      </c>
-      <c r="O11" s="4">
         <v>7.4989999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16152,19 +16127,19 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -16322,19 +16297,19 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -16492,19 +16467,19 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -16662,19 +16637,19 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
